--- a/tests/fixtures/template_fixture_alt.xlsx
+++ b/tests/fixtures/template_fixture_alt.xlsx
@@ -1802,7 +1802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:I4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1853,11 +1853,6 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
           <t>NOTES</t>
         </is>
       </c>
@@ -1893,8 +1888,7 @@
           <t>pass</t>
         </is>
       </c>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>iface note</t>
         </is>
@@ -1906,7 +1900,6 @@
       <c r="D4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
